--- a/public/templates/forms/A-090-PolicyAcknowledgmentRegister-FORM.xlsx
+++ b/public/templates/forms/A-090-PolicyAcknowledgmentRegister-FORM.xlsx
@@ -3,12 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="720" yWindow="780" windowWidth="29920" windowHeight="20380" tabRatio="500" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Register" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Register!$11:$11</definedName>
+  </definedNames>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -16,7 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="11">
     <font>
       <name val="Aptos"/>
@@ -196,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -256,6 +261,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -631,7 +639,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>« Add one row per active employee or contractor. Record each acknowledgment with its version and date, set Status, and set the next renewal date. The Summary flags anyone missing or overdue. »</t>
@@ -781,7 +789,6 @@
       <c r="B24" s="20" t="n"/>
       <c r="C24" s="13">
         <f>COUNTA(A12:A21)</f>
-        <v/>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
@@ -793,7 +800,6 @@
       <c r="B25" s="20" t="n"/>
       <c r="C25" s="13">
         <f>COUNTIF(E12:E21,"Current")</f>
-        <v/>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1">
@@ -805,7 +811,6 @@
       <c r="B26" s="20" t="n"/>
       <c r="C26" s="13">
         <f>COUNTIF(E12:E21,"Expiring")</f>
-        <v/>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1">
@@ -817,7 +822,6 @@
       <c r="B27" s="20" t="n"/>
       <c r="C27" s="13">
         <f>COUNTIF(E12:E21,"Missing")</f>
-        <v/>
       </c>
     </row>
     <row r="28" ht="15" customHeight="1">
@@ -834,7 +838,6 @@
       <c r="B29" s="20" t="n"/>
       <c r="C29" s="13">
         <f>COUNTIF(G12:G21,"&lt;"&amp;TODAY())</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="15" customHeight="1">
@@ -911,7 +914,7 @@
       <c r="F39" s="14" t="n"/>
       <c r="G39" s="14" t="n"/>
     </row>
-    <row r="40" ht="40" customHeight="1">
+    <row r="40" ht="50.5" customHeight="1">
       <c r="A40" s="12" t="inlineStr">
         <is>
           <t>[Approving official / title]</t>
@@ -1035,7 +1038,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1068,7 +1071,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="29.75" customHeight="1">
+    <row r="3" ht="34.7" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
           <t>Placeholder key:  [BRACKETED] = fill in   ·   « » = guidance to delete.  Classification, Source Authority, signatures and revision history live on the Register tab.</t>
@@ -1148,7 +1151,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="32" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Role / employment type</t>
@@ -1230,13 +1233,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>2026-02-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
+      <c r="D12" s="25">
+        <v>46063</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Next renewal due</t>
@@ -1252,10 +1253,8 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>2027-02-10</t>
-        </is>
+      <c r="D13" s="25">
+        <v>46428</v>
       </c>
     </row>
     <row r="15" ht="29.75" customHeight="1">
@@ -1341,6 +1340,6 @@
     <mergeCell ref="B22:D22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>